--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487999_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487999_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2341</v>
+        <v>3.0585</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5879</v>
+        <v>5.1596</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.3538</v>
+        <v>-2.1011</v>
       </c>
       <c r="G2" t="n">
         <v>1.6293</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7917</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1121</v>
+        <v>-0.5404</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6796</v>
+        <v>-0.4269</v>
       </c>
       <c r="V2" t="n">
         <v>1.2071</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4127</v>
+        <v>-0.0023</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5268</v>
+        <v>-1.2398</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9395</v>
+        <v>1.2375</v>
       </c>
       <c r="G3" t="n">
         <v>-2.8957</v>
@@ -688,13 +688,13 @@
         <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9803</v>
+        <v>0.5653</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9142</v>
+        <v>0.2012</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0661</v>
+        <v>0.3641</v>
       </c>
       <c r="V3" t="n">
         <v>0.9405</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2873</v>
+        <v>-0.175</v>
       </c>
       <c r="E4" t="n">
         <v>-0.3288</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0415</v>
+        <v>0.1538</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3842</v>
@@ -766,13 +766,13 @@
         <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2952</v>
+        <v>0.4075</v>
       </c>
       <c r="T4" t="n">
         <v>0.1176</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1776</v>
+        <v>0.2899</v>
       </c>
       <c r="V4" t="n">
         <v>0.6036</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2843</v>
+        <v>-1.0276</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1717</v>
+        <v>-1.6623</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8874</v>
+        <v>0.6347</v>
       </c>
       <c r="G5" t="n">
         <v>-1.7398</v>
@@ -844,13 +844,13 @@
         <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0591</v>
+        <v>0.3157</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4992</v>
+        <v>0.0102</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5582</v>
+        <v>0.3055</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4321</v>
+        <v>-1.5965</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1306</v>
+        <v>-1.2827</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3015</v>
+        <v>-0.3138</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2615</v>
+        <v>-1.9328</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1073</v>
+        <v>-1.6516</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8458</v>
+        <v>-0.2812</v>
       </c>
       <c r="J6" t="n">
-        <v>3.578</v>
+        <v>-1.1974</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3771</v>
+        <v>-1.3179</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2009</v>
+        <v>0.1205</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.3165</v>
+        <v>-0.7355</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2698</v>
+        <v>-0.3337</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0467</v>
+        <v>-0.4018</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.1627</v>
+        <v>0.5947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.9378</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7751</v>
+        <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>3.0726</v>
+        <v>0.0083</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9627</v>
+        <v>-0.0853</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.0936</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6036</v>
+        <v>-0.2666</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8701</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>S. OKUNGHAE FRANCIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7545</v>
+        <v>-1.8593</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3846</v>
+        <v>-1.0674</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3699</v>
+        <v>-0.7919</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9328</v>
+        <v>-1.273</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6516</v>
+        <v>-0.5153</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2812</v>
+        <v>-0.7577</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1974</v>
+        <v>0.0604</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3179</v>
+        <v>0.0202</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7355</v>
+        <v>-1.3333</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3337</v>
+        <v>-0.5355</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4018</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
         <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1498</v>
+        <v>-0.1899</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1872</v>
+        <v>-0.1367</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0374</v>
+        <v>-0.0533</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. OKUNGHAE FRANCIS</t>
+          <t>A. TORIL RAYO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9675</v>
+        <v>-2.8117</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2317</v>
+        <v>-1.2407</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7357</v>
+        <v>-1.571</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.273</v>
+        <v>-0.3996</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5153</v>
+        <v>-0.6713</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7577</v>
+        <v>0.2717</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0604</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0202</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3333</v>
+        <v>-0.3996</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5355</v>
+        <v>-0.6713</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.2717</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2981</v>
+        <v>-0.6103</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.301</v>
+        <v>-0.2496</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0029</v>
+        <v>-0.3607</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. TORIL RAYO</t>
+          <t>J. MORALES MUNOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8398</v>
+        <v>-3.1632</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2407</v>
+        <v>-1.9042</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.599</v>
+        <v>-1.259</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3996</v>
+        <v>-3.2364</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6713</v>
+        <v>-1.7003</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2717</v>
+        <v>-1.5361</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.8252</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.0429</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.2177</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3996</v>
+        <v>-4.0616</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6713</v>
+        <v>-2.7432</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2717</v>
+        <v>-1.3184</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3964</v>
+        <v>3.3698</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6383</v>
+        <v>-0.9268</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2496</v>
+        <v>-0.3596</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3888</v>
+        <v>-0.5673</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2071</v>
+        <v>0.6036</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MORALES MUNOZ</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2091</v>
+        <v>-3.4071</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7816</v>
+        <v>-2.1055</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4275</v>
+        <v>-1.3015</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2364</v>
+        <v>0.2615</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7003</v>
+        <v>1.1073</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5361</v>
+        <v>-0.8458</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8252</v>
+        <v>3.578</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0429</v>
+        <v>3.3771</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2177</v>
+        <v>0.2009</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.0616</v>
+        <v>-3.3165</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.7432</v>
+        <v>-2.2698</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3184</v>
+        <v>-1.0467</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3964</v>
+        <v>-4.1627</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9733</v>
+        <v>-6.9378</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3698</v>
+        <v>2.7751</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9726</v>
+        <v>1.0976</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2369</v>
+        <v>0.9877</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7357</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6036</v>
+        <v>-0.6036</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6036</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6624</v>
+        <v>-3.4939</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2325</v>
+        <v>-2.457</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4299</v>
+        <v>-1.0368</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2411</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7495</v>
+        <v>-0.5809</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0497</v>
+        <v>-0.2742</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6997</v>
+        <v>-0.3066</v>
       </c>
       <c r="V11" t="n">
         <v>0.337</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.7902</v>
+        <v>-14.4781</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.441099999999999</v>
+        <v>-8.128799999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.3489</v>
+        <v>-6.3491</v>
       </c>
       <c r="G12" t="n">
         <v>-15.2118</v>
@@ -1363,7 +1363,7 @@
         <v>-5.4329</v>
       </c>
       <c r="J12" t="n">
-        <v>4.698499999999999</v>
+        <v>4.698500000000001</v>
       </c>
       <c r="K12" t="n">
         <v>4.247599999999999</v>
@@ -1381,7 +1381,7 @@
         <v>-5.8842</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.0001000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.8488</v>
@@ -1390,13 +1390,13 @@
         <v>16.849</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1928</v>
+        <v>-0.8806999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6412000000000004</v>
+        <v>-0.3290999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5515999999999999</v>
+        <v>-0.5517000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>1.6145</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8663</v>
+        <v>5.2329</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5982</v>
+        <v>2.8851</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2681</v>
+        <v>2.3478</v>
       </c>
       <c r="G13" t="n">
         <v>4.3766</v>
@@ -1468,13 +1468,13 @@
         <v>3.1716</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4125</v>
+        <v>0.7791</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2262</v>
+        <v>0.5131</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1863</v>
+        <v>0.266</v>
       </c>
       <c r="V13" t="n">
         <v>0.8701</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8803</v>
+        <v>4.0945</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5639</v>
+        <v>2.6658</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3164</v>
+        <v>1.4288</v>
       </c>
       <c r="G14" t="n">
         <v>2.9451</v>
@@ -1546,13 +1546,13 @@
         <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7804</v>
+        <v>-0.5662</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.624</v>
+        <v>-0.5221</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1564</v>
+        <v>-0.0441</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2666</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8286</v>
+        <v>3.2195</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9119</v>
+        <v>3.0702</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9167</v>
+        <v>0.1492</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2956</v>
+        <v>2.1136</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6197</v>
+        <v>1.314</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3241</v>
+        <v>0.7997</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9922</v>
+        <v>3.3033</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5469</v>
+        <v>1.9774</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5547</v>
+        <v>1.3259</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6966</v>
+        <v>-1.1896</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9272</v>
+        <v>-0.6634</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7693</v>
+        <v>-0.5262</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3787</v>
+        <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5945</v>
+        <v>-0.2817</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3599</v>
+        <v>-0.233</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2346</v>
+        <v>-0.0487</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9877</v>
+        <v>2.9323</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8665</v>
+        <v>-0.9417</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1212</v>
+        <v>3.874</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1136</v>
+        <v>2.4744</v>
       </c>
       <c r="H16" t="n">
-        <v>1.314</v>
+        <v>0.5861</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7997</v>
+        <v>1.8884</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3033</v>
+        <v>1.8131</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9774</v>
+        <v>0.6324</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3259</v>
+        <v>1.1807</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1896</v>
+        <v>0.6613</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6634</v>
+        <v>-0.0463</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5262</v>
+        <v>0.7076</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3876</v>
+        <v>2.9733</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5135999999999999</v>
+        <v>0.4579</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4368</v>
+        <v>0.2186</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.2393</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8037</v>
+        <v>2.9287</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7379</v>
+        <v>1.6063</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5416</v>
+        <v>1.3224</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4744</v>
+        <v>2.2956</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5861</v>
+        <v>3.6197</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8884</v>
+        <v>-1.3241</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8131</v>
+        <v>3.9922</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6324</v>
+        <v>4.5469</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1807</v>
+        <v>-0.5547</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6613</v>
+        <v>-1.6966</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0463</v>
+        <v>-0.9272</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7076</v>
+        <v>-0.7693</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9733</v>
+        <v>2.3787</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3293</v>
+        <v>0.6946</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4223</v>
+        <v>0.0543</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.093</v>
+        <v>0.6403</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8725000000000001</v>
+        <v>1.122</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4618</v>
+        <v>0.7674</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4107</v>
+        <v>0.3546</v>
       </c>
       <c r="G18" t="n">
         <v>0.9320000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0595</v>
+        <v>0.1899</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1248</v>
+        <v>0.1808</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0653</v>
+        <v>0.0091</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3324</v>
+        <v>0.269</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1691</v>
+        <v>-0.3728</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5014</v>
+        <v>0.6418</v>
       </c>
       <c r="G19" t="n">
         <v>0.0185</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3139</v>
+        <v>0.2505</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4295</v>
+        <v>0.2258</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1157</v>
+        <v>0.0247</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>L. MORENO MORALES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.428</v>
+        <v>-0.1613</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3716</v>
+        <v>1.0068</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9436</v>
+        <v>-1.1681</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9906</v>
+        <v>1.3698</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9434</v>
+        <v>-1.4676</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9529</v>
+        <v>2.8373</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0084</v>
+        <v>2.548</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1256</v>
+        <v>-0.3966</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1172</v>
+        <v>2.9446</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0178</v>
+        <v>-1.1782</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1822</v>
+        <v>-1.0709</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1643</v>
+        <v>-0.1073</v>
       </c>
       <c r="P20" t="n">
         <v>-0.5947</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3787</v>
+        <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1167</v>
+        <v>0.2707</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>0.1744</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1863</v>
+        <v>0.0963</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9405</v>
+        <v>-1.2071</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.337</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6036</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. MORENO MORALES</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1049</v>
+        <v>-0.2804</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3956</v>
+        <v>-2.1679</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5005</v>
+        <v>1.8874</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3698</v>
+        <v>0.9906</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4676</v>
+        <v>1.9434</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8373</v>
+        <v>-0.9529</v>
       </c>
       <c r="J21" t="n">
-        <v>2.548</v>
+        <v>1.0084</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3966</v>
+        <v>2.1256</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9446</v>
+        <v>-1.1172</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1782</v>
+        <v>-0.0178</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0709</v>
+        <v>-0.1822</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1073</v>
+        <v>0.1643</v>
       </c>
       <c r="P21" t="n">
         <v>-0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3876</v>
+        <v>2.3787</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.2642</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4368</v>
+        <v>0.1341</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2361</v>
+        <v>0.1301</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2071</v>
+        <v>-0.9405</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2666</v>
+        <v>-0.337</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4737</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0549</v>
+        <v>-1.8231</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9239</v>
+        <v>-1.7202</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1309</v>
+        <v>-0.1029</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8108</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4512</v>
+        <v>-0.2193</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3744</v>
+        <v>-0.1706</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0487</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1936</v>
+        <v>-2.065</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2461</v>
+        <v>-0.4499</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9475</v>
+        <v>-1.6151</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4936</v>
@@ -2248,13 +2248,13 @@
         <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0965</v>
+        <v>0.0321</v>
       </c>
       <c r="T23" t="n">
-        <v>0.18</v>
+        <v>-0.0238</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2764</v>
+        <v>0.0559</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6036</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>14.7901</v>
+        <v>15.4691</v>
       </c>
       <c r="E24" t="n">
-        <v>6.349299999999999</v>
+        <v>6.349100000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>8.440799999999999</v>
+        <v>9.119899999999999</v>
       </c>
       <c r="G24" t="n">
         <v>15.2118</v>
       </c>
       <c r="H24" t="n">
-        <v>9.778799999999999</v>
+        <v>9.7788</v>
       </c>
       <c r="I24" t="n">
-        <v>5.433000000000001</v>
+        <v>5.433</v>
       </c>
       <c r="J24" t="n">
         <v>19.9105</v>
@@ -2308,13 +2308,13 @@
         <v>5.8841</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.698600000000001</v>
+        <v>-4.6986</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.247599999999999</v>
+        <v>-4.2476</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4510000000000002</v>
+        <v>-0.451</v>
       </c>
       <c r="P24" t="n">
         <v>-0.0001000000000003221</v>
@@ -2326,13 +2326,13 @@
         <v>16.849</v>
       </c>
       <c r="S24" t="n">
-        <v>1.1928</v>
+        <v>1.8718</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5514999999999998</v>
+        <v>0.5515999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6413</v>
+        <v>1.3202</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6146</v>
